--- a/Source/ReportDeptTourismSolution/CenIT.ReportTourism.Modules.CateModule/Contents/Modules/Cate/Templates/Mẫu import Doanh Nghiệp.xlsx
+++ b/Source/ReportDeptTourismSolution/CenIT.ReportTourism.Modules.CateModule/Contents/Modules/Cate/Templates/Mẫu import Doanh Nghiệp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\BaoCaoSoDuLich\trunk\Source\ReportDeptTourismSolution\CenIT.ReportTourism.Modules.CateModule\Contents\Modules\Cate\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Extends\Projects\Gits\BaoCao.SCT\Source\ReportDeptTourismSolution\CenIT.ReportTourism.Modules.CateModule\Contents\Modules\Cate\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4953781A-CF30-4B29-AA59-759BD31431A3}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FBB03AA-8D80-42D4-AEB9-AAE2AF105336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B1314383-1158-48B8-A1BD-509EC2ED8F11}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B1314383-1158-48B8-A1BD-509EC2ED8F11}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="71">
   <si>
     <t>TT</t>
   </si>
@@ -81,9 +81,6 @@
     <t>Xã/Phường</t>
   </si>
   <si>
-    <t>Huyện/Thị xã/Thành phố</t>
-  </si>
-  <si>
     <t>4200398240-001</t>
   </si>
   <si>
@@ -100,9 +97,6 @@
   </si>
   <si>
     <t>Lộc Thọ</t>
-  </si>
-  <si>
-    <t>Nha Trang</t>
   </si>
   <si>
     <t>02583526000</t>
@@ -205,13 +199,64 @@
   </si>
   <si>
     <t>Nguyễn Thị Kim Dinh</t>
+  </si>
+  <si>
+    <t>Loại hình doanh nghiệp</t>
+  </si>
+  <si>
+    <t>Công ty cổ phần</t>
+  </si>
+  <si>
+    <t>Công ty trách nhiệm hữu hạn</t>
+  </si>
+  <si>
+    <t>Doanh nghiệp có vốn đầu tư nước ngoài</t>
+  </si>
+  <si>
+    <t>Doanh nghiệp liên doanh</t>
+  </si>
+  <si>
+    <t>Ngành công nghiệp chính</t>
+  </si>
+  <si>
+    <t>Khu vực kinh tế</t>
+  </si>
+  <si>
+    <t>Kinh tế ngoài nhà nước</t>
+  </si>
+  <si>
+    <t>Sản xuất, chế biến thực phẩm</t>
+  </si>
+  <si>
+    <t>Sản xuất sản phẩm thuốc lá</t>
+  </si>
+  <si>
+    <t>Sản xuất đồ uống</t>
+  </si>
+  <si>
+    <t>Sản xuất trang phục</t>
+  </si>
+  <si>
+    <t>Nhóm doanh nghiệp</t>
+  </si>
+  <si>
+    <t>Doanh nghiệp sản xuất, kinh doanh</t>
+  </si>
+  <si>
+    <t>Doanh nghiệp thương mại, dịch vụ</t>
+  </si>
+  <si>
+    <t>Tỉnh/Thành Phố</t>
+  </si>
+  <si>
+    <t>Khánh Hòa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -382,52 +427,16 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -460,6 +469,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -483,9 +519,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -523,7 +559,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -629,7 +665,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -771,7 +807,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -779,266 +815,334 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A52B595B-C7DA-4DFD-BFC8-3CD8396DC904}">
-  <dimension ref="A1:N6"/>
-  <sheetFormatPr defaultColWidth="16.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R6"/>
+  <sheetFormatPr defaultColWidth="16.28515625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" customWidth="1"/>
-    <col min="2" max="4" width="16.28515625" style="1"/>
-    <col min="5" max="5" width="17.28515625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="16.28515625" style="1"/>
+    <col min="2" max="8" width="16.28515625" style="1"/>
+    <col min="9" max="9" width="17.28515625" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="16.28515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="5" t="s">
+      <c r="N1" s="21"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="7"/>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:14" s="18" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="12"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="17" t="s">
+    <row r="2" spans="1:18" s="6" customFormat="1" ht="31.5">
+      <c r="A2" s="19"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="J2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="K2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="L2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="47.25">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="P3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="10"/>
+    </row>
+    <row r="4" spans="1:18" ht="63">
+      <c r="A4" s="4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4">
+        <v>4200466765</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="P4" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q4" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R4" s="10"/>
+    </row>
+    <row r="5" spans="1:18" ht="47.25">
+      <c r="A5" s="4">
         <v>3</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="B5" s="4">
+        <v>4201872752</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="P5" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q5" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="R5" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="63">
+      <c r="A6" s="4">
         <v>4</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="16">
-        <v>1</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="16" t="s">
+      <c r="B6" s="4">
+        <v>4201215362</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="23"/>
-      <c r="N3" s="22"/>
-    </row>
-    <row r="4" spans="1:14" ht="63" x14ac:dyDescent="0.25">
-      <c r="A4" s="16">
-        <v>2</v>
-      </c>
-      <c r="B4" s="16">
-        <v>4200466765</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="N4" s="22"/>
-    </row>
-    <row r="5" spans="1:14" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
-        <v>3</v>
-      </c>
-      <c r="B5" s="16">
-        <v>4201872752</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="K5" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="L5" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="M5" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N5" s="25" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="63" x14ac:dyDescent="0.25">
-      <c r="A6" s="16">
-        <v>4</v>
-      </c>
-      <c r="B6" s="16">
-        <v>4201215362</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="19" t="s">
+      <c r="L6" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="M6" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="N6" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="G6" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="20" t="s">
+      <c r="O6" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="P6" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="K6" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="M6" s="23"/>
-      <c r="N6" s="22"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="E1:H1"/>
+  <mergeCells count="11">
+    <mergeCell ref="I1:L1"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:R1"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="J3" r:id="rId1" xr:uid="{5E282E20-F862-4139-9471-352478CD78B6}"/>
-    <hyperlink ref="K3" r:id="rId2" xr:uid="{524301EF-7878-46D7-A3DF-969ABA91A220}"/>
-    <hyperlink ref="J4" r:id="rId3" xr:uid="{1F266255-A520-4F18-B95E-815496CB1DCF}"/>
-    <hyperlink ref="K4" r:id="rId4" display="gm@isenahotel.com\" xr:uid="{E5CB63EF-0E34-4427-99DF-7C2FF8BE50BA}"/>
-    <hyperlink ref="J5" r:id="rId5" xr:uid="{A569A91E-B73F-49A3-9890-13D92D0EE571}"/>
-    <hyperlink ref="K5" r:id="rId6" xr:uid="{11F5A37E-AF7C-4C6F-9FA0-150252A8248C}"/>
-    <hyperlink ref="N5" r:id="rId7" xr:uid="{3C396D1A-3B1A-4B0E-927D-58EFE4C33A65}"/>
-    <hyperlink ref="J6" r:id="rId8" xr:uid="{1C3B0790-732C-4F43-BD42-BE91F6E9E744}"/>
+    <hyperlink ref="N3" r:id="rId1" xr:uid="{5E282E20-F862-4139-9471-352478CD78B6}"/>
+    <hyperlink ref="O3" r:id="rId2" xr:uid="{524301EF-7878-46D7-A3DF-969ABA91A220}"/>
+    <hyperlink ref="N4" r:id="rId3" xr:uid="{1F266255-A520-4F18-B95E-815496CB1DCF}"/>
+    <hyperlink ref="O4" r:id="rId4" display="gm@isenahotel.com\" xr:uid="{E5CB63EF-0E34-4427-99DF-7C2FF8BE50BA}"/>
+    <hyperlink ref="N5" r:id="rId5" xr:uid="{A569A91E-B73F-49A3-9890-13D92D0EE571}"/>
+    <hyperlink ref="O5" r:id="rId6" xr:uid="{11F5A37E-AF7C-4C6F-9FA0-150252A8248C}"/>
+    <hyperlink ref="R5" r:id="rId7" xr:uid="{3C396D1A-3B1A-4B0E-927D-58EFE4C33A65}"/>
+    <hyperlink ref="N6" r:id="rId8" xr:uid="{1C3B0790-732C-4F43-BD42-BE91F6E9E744}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId9"/>
